--- a/IRP_Agent_더미고객_9Cases_v3.xlsx
+++ b/IRP_Agent_더미고객_9Cases_v3.xlsx
@@ -3497,10 +3497,10 @@
         <x:v>0.4266666666666667</x:v>
       </x:c>
       <x:c r="I28" s="24" t="n">
-        <x:v>45918</x:v>
+        <x:v>45939</x:v>
       </x:c>
       <x:c r="J28" s="24" t="n">
-        <x:v>46283</x:v>
+        <x:v>46304</x:v>
       </x:c>
       <x:c r="K28" t="str">
         <x:v>매우낮은위험</x:v>

--- a/IRP_Agent_더미고객_9Cases_v3.xlsx
+++ b/IRP_Agent_더미고객_9Cases_v3.xlsx
@@ -1130,6 +1130,20 @@
         <x:v>최근상담일 공란 고객은 상담이력 없음</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>TAX_AND_ISA</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>총급여</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>연간 총급여(원). 5,500만원 이하 16.5% · 초과 13.2% (지방소득세 포함)</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>원본 9Cases 에 없던 컬럼 — 세액공제 갈래를 시연·테스트하려고 부여한 값</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
@@ -4731,6 +4745,7 @@
     <x:col min="11" max="11" width="11.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="10.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14.13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -4790,6 +4805,9 @@
       <x:c r="M2" s="14" t="str">
         <x:v>ISA기관구분</x:v>
       </x:c>
+      <x:c r="N2" s="14" t="str">
+        <x:v>총급여</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -4829,6 +4847,9 @@
       <x:c r="M3" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N3" s="20" t="n">
+        <x:v>38000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -4868,6 +4889,9 @@
       <x:c r="M4" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N4" s="20" t="n">
+        <x:v>55000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -4907,6 +4931,9 @@
       <x:c r="M5" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N5" s="20" t="n">
+        <x:v>78000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -4946,6 +4973,9 @@
       <x:c r="M6" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N6" s="20" t="n">
+        <x:v>51000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -4985,6 +5015,9 @@
       <x:c r="M7" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N7" s="20" t="n">
+        <x:v>120000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -5026,6 +5059,9 @@
       <x:c r="M8" t="str">
         <x:v>타행</x:v>
       </x:c>
+      <x:c r="N8" s="20" t="n">
+        <x:v>95000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
@@ -5065,6 +5101,9 @@
       <x:c r="M9" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N9" s="20" t="n">
+        <x:v>66000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -5104,6 +5143,9 @@
       <x:c r="M10" t="str">
         <x:v>없음</x:v>
       </x:c>
+      <x:c r="N10" s="20" t="n">
+        <x:v>42000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -5144,6 +5186,9 @@
       </x:c>
       <x:c r="M11" t="str">
         <x:v>당행</x:v>
+      </x:c>
+      <x:c r="N11" s="20" t="n">
+        <x:v>24000000</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/IRP_Agent_더미고객_9Cases_v3.xlsx
+++ b/IRP_Agent_더미고객_9Cases_v3.xlsx
@@ -757,7 +757,7 @@
         <x:v>만기도래 / 연금개시 요건충족 후 미개시</x:v>
       </x:c>
       <x:c r="H9" t="str">
-        <x:v>2개 복합: 연금개시 가능 고객에게 예금 만기까지 겹쳐 수령·운용을 함께 점검하는 케이스.</x:v>
+        <x:v>2개 복합: 연금개시 가능 고객에게 예금 만기까지 겹쳐 수령·운용을 함께 점검하는 케이스. 디폴트옵션 미설정 · 연금저축펀드 보유 상태를 함께 둔다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1142,6 +1142,20 @@
       </x:c>
       <x:c r="D20" t="str">
         <x:v>원본 9Cases 에 없던 컬럼 — 세액공제 갈래를 시연·테스트하려고 부여한 값</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>TAX_AND_ISA</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>연금저축보유여부</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>연금저축(연금저축펀드 포함) 계좌 보유 여부 Y/N. 비어 있으면 미확인</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>원본 9Cases 에 없던 컬럼 — 오세훈(193482-6012375)에만 Y 부여, 나머지는 미확인으로 비워 둠</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2222,10 +2236,10 @@
         <x:v>0.062</x:v>
       </x:c>
       <x:c r="Q9" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="R9" t="str">
-        <x:v>저위험</x:v>
+        <x:v>미설정</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4746,6 +4760,7 @@
     <x:col min="12" max="12" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="10.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.13" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -4808,6 +4823,9 @@
       <x:c r="N2" s="14" t="str">
         <x:v>총급여</x:v>
       </x:c>
+      <x:c r="O2" s="14" t="str">
+        <x:v>연금저축보유여부</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -5103,6 +5121,9 @@
       </x:c>
       <x:c r="N9" s="20" t="n">
         <x:v>66000000</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="10">

--- a/IRP_Agent_더미고객_9Cases_v3.xlsx
+++ b/IRP_Agent_더미고객_9Cases_v3.xlsx
@@ -3548,7 +3548,7 @@
         <x:v>193482-6012375</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년)</x:v>
+        <x:v>KB라이프생명 퇴직연금 이율보증형보험(3년)</x:v>
       </x:c>
       <x:c r="C29" t="str">
         <x:v>GIC</x:v>
